--- a/buildplan_generator/output/25-073 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-073 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,12 +70,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-072, 25-074, 25-054, 23-040, 25-032</t>
+          <t>25-072, 23-045, 23-032, 23-047, 23-048</t>
         </is>
       </c>
     </row>
@@ -635,17 +628,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +713,8 @@
       <c r="E9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>4.5</v>
+      <c r="F9" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>3.0-7.5</t>
+          <t>ratio=0.75 (0.33-1.17)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +750,8 @@
       <c r="E10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>12</v>
+      <c r="F10" s="9" t="n">
+        <v>7.2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>6.5-14.5</t>
+          <t>ratio=0.90 (0.33-1.10)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -796,8 +787,8 @@
       <c r="E11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>1.2</v>
+      <c r="F11" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -806,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>1.0-5.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -833,8 +824,8 @@
       <c r="E12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>1.8</v>
+      <c r="F12" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -843,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -870,7 +861,7 @@
       <c r="E13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -880,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.00 (0.75-1.00)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -907,8 +898,8 @@
       <c r="E14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>5.2</v>
+      <c r="F14" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -917,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>4.0-7.0</t>
+          <t>ratio=1.12 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -944,8 +935,8 @@
       <c r="E15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>2.5</v>
+      <c r="F15" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -954,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.17 (0.83-2.00)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -982,16 +973,16 @@
         <v>1</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1035,8 +1026,8 @@
       <c r="E18" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F18" s="10" t="n">
-        <v>26.5</v>
+      <c r="F18" s="9" t="n">
+        <v>33.6</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1045,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>14.0-39.5</t>
+          <t>ratio=1.20 (0.80-1.40)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1073,16 +1064,16 @@
         <v>16</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>3.5-20.2</t>
+          <t>ratio=0.22 (n=1)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1126,8 +1117,8 @@
       <c r="E21" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>3.5</v>
+      <c r="F21" s="9" t="n">
+        <v>7.4</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1136,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>2.0-46.5</t>
+          <t>ratio=0.93 (0.25-1.00)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1163,8 +1154,8 @@
       <c r="E22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>2.5</v>
+      <c r="F22" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1173,7 +1164,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1217,7 +1208,7 @@
       <c r="E24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -1227,7 +1218,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1255,16 +1246,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1309,12 +1300,12 @@
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1341,8 +1332,8 @@
       <c r="E28" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>15</v>
+      <c r="F28" s="9" t="n">
+        <v>28.5</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1351,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>5.0-27.0</t>
+          <t>ratio=0.79 (0.61-1.80)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1378,8 +1369,8 @@
       <c r="E29" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>12</v>
+      <c r="F29" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1388,7 +1379,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>4.0-20.0</t>
+          <t>ratio=0.67 (0.58-1.33)</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1433,16 +1424,16 @@
         <v>11</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>11.0-13.5</t>
+          <t>ratio=1.23 (n=1)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1467,17 +1458,15 @@
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
-      <c r="F32" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1504,8 +1493,8 @@
       <c r="E33" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>3</v>
+      <c r="F33" s="9" t="n">
+        <v>3.4</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1514,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>2.0-5.5</t>
+          <t>ratio=1.69 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1541,8 +1530,8 @@
       <c r="E34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>3</v>
+      <c r="F34" s="9" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1551,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>1.0-6.0</t>
+          <t>ratio=4.38 (0.50-4.62)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1578,8 +1567,8 @@
       <c r="E35" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>7.8</v>
+      <c r="F35" s="9" t="n">
+        <v>9.6</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1588,7 +1577,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>ratio=1.60 (1.00-1.98)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1632,8 +1621,8 @@
       <c r="E37" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>8</v>
+      <c r="F37" s="9" t="n">
+        <v>7.3</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1642,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>6.2-33.0</t>
+          <t>ratio=1.04 (0.89-1.11)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1686,8 +1675,8 @@
       <c r="E39" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>10</v>
+      <c r="F39" s="9" t="n">
+        <v>22.8</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1696,7 +1685,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>6.5-19.0</t>
+          <t>ratio=1.62 (1.08-1.81)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1723,8 +1712,8 @@
       <c r="E40" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>5</v>
+      <c r="F40" s="9" t="n">
+        <v>21.1</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1733,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>4.0-20.2</t>
+          <t>ratio=1.50 (1.19-1.62)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1760,8 +1749,8 @@
       <c r="E41" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F41" s="10" t="n">
-        <v>11.5</v>
+      <c r="F41" s="9" t="n">
+        <v>14.4</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1770,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>5.0-23.0</t>
+          <t>ratio=1.03 (0.50-1.21)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1798,16 +1787,16 @@
         <v>12</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>4.0-5.5</t>
+          <t>ratio=0.46 (n=1)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1835,16 +1824,16 @@
         <v>12</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>4.0-10.2</t>
+          <t>ratio=0.85 (n=1)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1872,16 +1861,16 @@
         <v>2</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=2.88 (n=2)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1906,17 +1895,15 @@
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
-      <c r="F45" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1943,8 +1930,8 @@
       <c r="E46" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>8</v>
+      <c r="F46" s="9" t="n">
+        <v>11.2</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1953,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>4.5-13.0</t>
+          <t>ratio=1.25 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1980,7 +1967,7 @@
       <c r="E47" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F47" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -1990,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>8.0-24.0</t>
+          <t>ratio=1.20 (0.62-2.25)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2017,8 +2004,8 @@
       <c r="E48" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>2.9</v>
+      <c r="F48" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2027,7 +2014,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>2.0-5.5</t>
+          <t>ratio=3.50 (0.92-5.00)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2071,8 +2058,8 @@
       <c r="E50" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>20.8</v>
+      <c r="F50" s="9" t="n">
+        <v>16.9</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2081,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>15.0-22.5</t>
+          <t>ratio=0.80 (0.73-1.07)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2109,16 +2096,16 @@
         <v>5</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.5</t>
+          <t>ratio=0.90 (n=2)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2145,8 +2132,8 @@
       <c r="E52" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F52" s="10" t="n">
-        <v>19.5</v>
+      <c r="F52" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2155,7 +2142,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>6.5-44.0</t>
+          <t>ratio=0.67 (0.50-0.97)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2182,8 +2169,8 @@
       <c r="E53" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F53" s="10" t="n">
-        <v>6</v>
+      <c r="F53" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2192,7 +2179,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>2.5-7.5</t>
+          <t>ratio=0.58 (0.42-1.00)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2219,8 +2206,8 @@
       <c r="E54" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F54" s="10" t="n">
-        <v>10</v>
+      <c r="F54" s="9" t="n">
+        <v>9.4</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2229,7 +2216,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>7.0-32.0</t>
+          <t>ratio=0.78 (0.58-1.53)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2256,7 +2243,7 @@
       <c r="E55" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="10" t="n">
+      <c r="F55" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -2266,7 +2253,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2310,17 +2297,17 @@
       <c r="E57" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="11" t="n">
-        <v>2</v>
+      <c r="F57" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=2.50 (1.00-5.00)</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2345,17 +2332,15 @@
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
-      <c r="F58" s="11" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>1.5-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2399,8 +2384,8 @@
       <c r="E60" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F60" s="10" t="n">
-        <v>3.5</v>
+      <c r="F60" s="9" t="n">
+        <v>6.8</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2409,7 +2394,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>1.0-10.0</t>
+          <t>ratio=2.25 (0.50-4.00)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2436,8 +2421,8 @@
       <c r="E61" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F61" s="10" t="n">
-        <v>21</v>
+      <c r="F61" s="9" t="n">
+        <v>16.3</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2446,7 +2431,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>7.0-33.0</t>
+          <t>ratio=1.17 (0.58-1.28)</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2474,12 +2459,12 @@
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2506,8 +2491,8 @@
       <c r="E63" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="F63" s="10" t="n">
-        <v>59</v>
+      <c r="F63" s="9" t="n">
+        <v>64</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
@@ -2516,7 +2501,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>25.5-96.2</t>
+          <t>ratio=1.33 (0.31-1.88)</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2544,12 +2529,12 @@
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2593,8 +2578,8 @@
       <c r="E66" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="10" t="n">
-        <v>9</v>
+      <c r="F66" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2603,7 +2588,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>4.8-11.8</t>
+          <t>ratio=1.75 (0.67-3.67)</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2631,12 +2616,12 @@
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2663,8 +2648,8 @@
       <c r="E68" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F68" s="10" t="n">
-        <v>10</v>
+      <c r="F68" s="9" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2673,7 +2658,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>7.0-16.0</t>
+          <t>ratio=1.75 (0.75-3.20)</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2687,7 +2672,7 @@
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>381.5</v>
+        <v>425.7</v>
       </c>
     </row>
   </sheetData>
@@ -2755,7 +2740,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-072, 25-074, 25-054, 23-040, 25-032</t>
+          <t>25-072, 23-045, 23-032, 23-047, 23-048</t>
         </is>
       </c>
     </row>
@@ -4430,28 +4415,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-074</t>
+          <t>23-045</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-054</t>
+          <t>23-032</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-040</t>
+          <t>23-047</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-032</t>
+          <t>23-048</t>
         </is>
       </c>
     </row>
@@ -4506,23 +4491,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4540,19 +4521,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>23-040, 25-032, 25-054, 25-072</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4566,7 +4543,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4575,12 +4552,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.0-7.5</t>
+          <t>ratio=0.75 (0.33-1.17)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4573,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4605,12 +4582,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.5-14.5</t>
+          <t>ratio=0.90 (0.33-1.10)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4603,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4635,12 +4612,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.0-5.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4633,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4665,12 +4642,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4695,12 +4672,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.00 (0.75-1.00)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4693,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4725,12 +4702,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.0-7.0</t>
+          <t>ratio=1.12 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4723,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4755,12 +4732,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.17 (0.83-2.00)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4776,21 +4753,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-072, 25-032, 23-040</t>
+          <t>25-072</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4783,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26.5</v>
+        <v>33.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4815,12 +4792,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.0-39.5</t>
+          <t>ratio=1.20 (0.80-1.40)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4836,21 +4813,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.5-20.2</t>
+          <t>ratio=0.22 (n=1)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032</t>
+          <t>25-072</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4843,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4875,12 +4852,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.0-46.5</t>
+          <t>ratio=0.93 (0.25-1.00)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4873,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4905,12 +4882,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4912,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4956,21 +4933,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-072, 25-032, 23-040</t>
+          <t>25-072</t>
         </is>
       </c>
     </row>
@@ -4990,19 +4967,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>23-040, 25-032, 25-054, 25-072, 25-074</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5016,7 +4989,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>28.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5025,12 +4998,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.0-27.0</t>
+          <t>ratio=0.79 (0.61-1.80)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5019,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5055,12 +5028,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.0-20.0</t>
+          <t>ratio=0.67 (0.58-1.33)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5076,21 +5049,21 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11.0-13.5</t>
+          <t>ratio=1.23 (n=1)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-072, 25-032, 23-040</t>
+          <t>25-072</t>
         </is>
       </c>
     </row>
@@ -5106,23 +5079,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5136,7 +5105,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5145,12 +5114,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2.0-5.5</t>
+          <t>ratio=1.69 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5135,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5175,12 +5144,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.0-6.0</t>
+          <t>ratio=4.38 (0.50-4.62)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5165,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5205,12 +5174,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>ratio=1.60 (1.00-1.98)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5195,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5235,12 +5204,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6.2-33.0</t>
+          <t>ratio=1.04 (0.89-1.11)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-072, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045</t>
         </is>
       </c>
     </row>
@@ -5256,23 +5225,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5286,7 +5251,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>22.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5295,12 +5260,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.5-19.0</t>
+          <t>ratio=1.62 (1.08-1.81)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5281,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>21.1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5325,12 +5290,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.0-20.2</t>
+          <t>ratio=1.50 (1.19-1.62)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5311,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11.5</v>
+        <v>14.4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5355,12 +5320,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5.0-23.0</t>
+          <t>ratio=1.03 (0.50-1.21)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045</t>
         </is>
       </c>
     </row>
@@ -5376,21 +5341,21 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.0-5.5</t>
+          <t>ratio=0.46 (n=1)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-072, 25-032, 23-040</t>
+          <t>25-072</t>
         </is>
       </c>
     </row>
@@ -5406,21 +5371,21 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.0-10.2</t>
+          <t>ratio=0.85 (n=1)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-072, 25-032, 23-040</t>
+          <t>25-072</t>
         </is>
       </c>
     </row>
@@ -5436,21 +5401,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=2.88 (n=2)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>23-048, 23-047</t>
         </is>
       </c>
     </row>
@@ -5466,23 +5431,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5496,7 +5457,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5505,12 +5466,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.5-13.0</t>
+          <t>ratio=1.25 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5535,12 +5496,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8.0-24.0</t>
+          <t>ratio=1.20 (0.62-2.25)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5517,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5565,12 +5526,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2.0-5.5</t>
+          <t>ratio=3.50 (0.92-5.00)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5547,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>20.8</v>
+        <v>16.9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5595,12 +5556,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15.0-22.5</t>
+          <t>ratio=0.80 (0.73-1.07)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-072, 25-054, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045</t>
         </is>
       </c>
     </row>
@@ -5616,21 +5577,21 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.0-4.5</t>
+          <t>ratio=0.90 (n=2)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-032</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5607,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5655,12 +5616,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6.5-44.0</t>
+          <t>ratio=0.67 (0.50-0.97)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5637,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5685,12 +5646,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2.5-7.5</t>
+          <t>ratio=0.58 (0.42-1.00)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5667,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5715,12 +5676,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.0-32.0</t>
+          <t>ratio=0.78 (0.58-1.53)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5706,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5766,21 +5727,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=2.50 (1.00-5.00)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5796,23 +5757,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5-1.5</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5826,7 +5783,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5835,12 +5792,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.0-10.0</t>
+          <t>ratio=2.25 (0.50-4.00)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5813,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>21</v>
+        <v>16.3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5865,12 +5822,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.0-33.0</t>
+          <t>ratio=1.17 (0.58-1.28)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5890,19 +5847,15 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>23-040, 25-032, 25-054, 25-072, 25-074</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5916,7 +5869,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5925,12 +5878,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>25.5-96.2</t>
+          <t>ratio=1.33 (0.31-1.88)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5950,19 +5903,15 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>23-040, 25-032, 25-054, 25-072, 25-074</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5976,7 +5925,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5985,12 +5934,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4.8-11.8</t>
+          <t>ratio=1.75 (0.67-3.67)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -6010,19 +5959,15 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>23-040, 25-032, 25-054, 25-072, 25-074</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6036,7 +5981,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6045,12 +5990,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>7.0-16.0</t>
+          <t>ratio=1.75 (0.75-3.20)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-074, 25-072, 25-054, 25-032, 23-040</t>
+          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-073 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-073 GENERATED BUILD PLAN.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-072, 23-045, 23-032, 23-047, 23-048</t>
+          <t>25-072, 23-032, 23-040, 23-045, 23-047</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (1.00-2.00)</t>
+          <t>ratio=1.25 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.83-2.00)</t>
+          <t>ratio=1.00 (0.67-2.00)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -973,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>ratio=1.33 (n=2)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.80-1.40)</t>
+          <t>ratio=1.20 (0.80-1.32)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.93 (0.25-1.00)</t>
+          <t>ratio=0.93 (0.25-1.17)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1370,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.58-1.33)</t>
+          <t>ratio=1.00 (0.62-1.33)</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1424,7 +1424,7 @@
         <v>11</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.23 (n=1)</t>
+          <t>ratio=1.30 (n=2)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.69 (1.00-2.50)</t>
+          <t>ratio=1.78 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1531,7 +1531,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=4.38 (0.50-4.62)</t>
+          <t>ratio=1.00 (0.50-4.38)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1622,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.04 (0.89-1.11)</t>
+          <t>ratio=1.10 (0.89-1.32)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1676,7 +1676,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>22.8</v>
+        <v>19</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.62 (1.08-1.81)</t>
+          <t>ratio=1.36 (0.93-1.71)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1713,7 +1713,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.19-1.62)</t>
+          <t>ratio=1.47 (1.19-1.56)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1750,7 +1750,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.03 (0.50-1.21)</t>
+          <t>ratio=1.08 (0.50-1.67)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1787,7 +1787,7 @@
         <v>12</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.46 (n=1)</t>
+          <t>ratio=0.73 (n=2)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1824,7 +1824,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>10.2</v>
+        <v>14.7</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.85 (n=1)</t>
+          <t>ratio=1.23 (n=2)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1861,7 +1861,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.88 (n=2)</t>
+          <t>ratio=1.88 (n=2)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1931,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>11.2</v>
+        <v>13</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-2.50)</t>
+          <t>ratio=1.44 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1968,7 +1968,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>16.8</v>
+        <v>19.7</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.62-2.25)</t>
+          <t>ratio=1.41 (0.80-2.25)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2059,7 +2059,7 @@
         <v>21</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>16.9</v>
+        <v>20</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.73-1.07)</t>
+          <t>ratio=0.95 (0.73-1.30)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2095,17 +2095,17 @@
       <c r="E51" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="9" t="n">
         <v>4.5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (n=2)</t>
+          <t>ratio=0.90 (0.80-1.00)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2170,7 +2170,7 @@
         <v>6</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.58 (0.42-1.00)</t>
+          <t>ratio=0.88 (0.42-1.25)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.58-1.53)</t>
+          <t>ratio=0.78 (0.58-1.75)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.58-1.28)</t>
+          <t>ratio=1.17 (0.64-1.28)</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2579,7 +2579,7 @@
         <v>4</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.75 (0.67-3.67)</t>
+          <t>ratio=2.34 (1.33-3.67)</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2649,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.75 (0.75-3.20)</t>
+          <t>ratio=1.96 (0.75-3.20)</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>425.7</v>
+        <v>443.3</v>
       </c>
     </row>
   </sheetData>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-072, 23-045, 23-032, 23-047, 23-048</t>
+          <t>25-072, 23-032, 23-040, 23-045, 23-047</t>
         </is>
       </c>
     </row>
@@ -4415,28 +4415,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-045</t>
+          <t>23-032</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-032</t>
+          <t>23-040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-047</t>
+          <t>23-045</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-048</t>
+          <t>23-047</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4702,12 +4702,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.12 (1.00-2.00)</t>
+          <t>ratio=1.25 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4732,12 +4732,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.83-2.00)</t>
+          <t>ratio=1.00 (0.67-2.00)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>ratio=1.33 (n=2)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-072</t>
+          <t>25-072, 23-040</t>
         </is>
       </c>
     </row>
@@ -4792,12 +4792,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.80-1.40)</t>
+          <t>ratio=1.20 (0.80-1.32)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=0.93 (0.25-1.00)</t>
+          <t>ratio=0.93 (0.25-1.17)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-072</t>
+          <t>25-072, 23-040</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5028,12 +5028,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.58-1.33)</t>
+          <t>ratio=1.00 (0.62-1.33)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5058,12 +5058,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.23 (n=1)</t>
+          <t>ratio=1.30 (n=2)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-072</t>
+          <t>25-072, 23-040</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.69 (1.00-2.50)</t>
+          <t>ratio=1.78 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=4.38 (0.50-4.62)</t>
+          <t>ratio=1.00 (0.50-4.38)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=1.04 (0.89-1.11)</t>
+          <t>ratio=1.10 (0.89-1.32)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045</t>
+          <t>25-072, 23-047, 23-045, 23-040</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>22.8</v>
+        <v>19</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=1.62 (1.08-1.81)</t>
+          <t>ratio=1.36 (0.93-1.71)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,12 +5290,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.19-1.62)</t>
+          <t>ratio=1.47 (1.19-1.56)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045</t>
+          <t>25-072, 23-047, 23-045, 23-040</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5320,12 +5320,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.03 (0.50-1.21)</t>
+          <t>ratio=1.08 (0.50-1.67)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045</t>
+          <t>25-072, 23-047, 23-045, 23-040</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=0.46 (n=1)</t>
+          <t>ratio=0.73 (n=2)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-072</t>
+          <t>25-072, 23-040</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10.2</v>
+        <v>14.7</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=0.85 (n=1)</t>
+          <t>ratio=1.23 (n=2)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-072</t>
+          <t>25-072, 23-040</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=2.88 (n=2)</t>
+          <t>ratio=1.88 (n=2)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>23-048, 23-047</t>
+          <t>23-047, 23-040</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11.2</v>
+        <v>13</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-2.50)</t>
+          <t>ratio=1.44 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.8</v>
+        <v>19.7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.62-2.25)</t>
+          <t>ratio=1.41 (0.80-2.25)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.9</v>
+        <v>20</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5556,12 +5556,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.73-1.07)</t>
+          <t>ratio=0.95 (0.73-1.30)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045</t>
+          <t>25-072, 23-047, 23-045, 23-040</t>
         </is>
       </c>
     </row>
@@ -5581,17 +5581,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=0.90 (n=2)</t>
+          <t>ratio=0.90 (0.80-1.00)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-072, 23-032</t>
+          <t>25-072, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=0.58 (0.42-1.00)</t>
+          <t>ratio=0.88 (0.42-1.25)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.58-1.53)</t>
+          <t>ratio=0.78 (0.58-1.75)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-045, 23-032</t>
+          <t>25-072, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5822,12 +5822,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.58-1.28)</t>
+          <t>ratio=1.17 (0.64-1.28)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=1.75 (0.67-3.67)</t>
+          <t>ratio=2.34 (1.33-3.67)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5990,12 +5990,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ratio=1.75 (0.75-3.20)</t>
+          <t>ratio=1.96 (0.75-3.20)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-072, 23-048, 23-047, 23-045, 23-032</t>
+          <t>25-072, 23-047, 23-045, 23-032</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-073 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-073 GENERATED BUILD PLAN.xlsx
@@ -80,8 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-072, 23-032, 23-040, 23-045, 23-047</t>
+          <t>25-072, 23-045, 23-047, 23-046, 23-048</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -664,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.33-1.17)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.33-1.10)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -788,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -825,7 +825,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -862,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -899,7 +899,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-2.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-2.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -972,17 +972,17 @@
       <c r="E16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>1.3</v>
+      <c r="F16" s="9" t="n">
+        <v>0.7</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.33 (n=2)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1027,7 +1027,7 @@
         <v>28</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>33.6</v>
+        <v>24.9</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.80-1.32)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1063,17 +1063,17 @@
       <c r="E19" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>3.5</v>
+      <c r="F19" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.22 (n=1)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1118,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.93 (0.25-1.17)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1155,7 +1155,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1209,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1245,17 +1245,17 @@
       <c r="E25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>2</v>
+      <c r="F25" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1300,12 +1300,12 @@
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1333,7 +1333,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>28.5</v>
+        <v>19.1</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.79 (0.61-1.80)</t>
+          <t>group_total:37h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1370,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>24</v>
+        <v>17.7</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.33)</t>
+          <t>group_total:37h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1423,17 +1423,17 @@
       <c r="E31" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>14.3</v>
+      <c r="F31" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.30 (n=2)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1461,12 +1461,12 @@
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.78 (1.00-2.50)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1531,7 +1531,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-4.38)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1568,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.60 (1.00-1.98)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1622,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>7.7</v>
+        <v>12.8</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.10 (0.89-1.32)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1676,7 +1676,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.36 (0.93-1.71)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1713,7 +1713,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>20.6</v>
+        <v>9.6</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.47 (1.19-1.56)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1750,7 +1750,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>15.1</v>
+        <v>11.3</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.08 (0.50-1.67)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1786,17 +1786,17 @@
       <c r="E42" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F42" s="10" t="n">
-        <v>8.800000000000001</v>
+      <c r="F42" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.73 (n=2)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1823,17 +1823,17 @@
       <c r="E43" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>14.7</v>
+      <c r="F43" s="9" t="n">
+        <v>4.4</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.23 (n=2)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1860,17 +1860,17 @@
       <c r="E44" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>3.8</v>
+      <c r="F44" s="9" t="n">
+        <v>3.7</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.88 (n=2)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1898,12 +1898,12 @@
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1931,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.44 (1.00-2.50)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1968,7 +1968,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>19.7</v>
+        <v>22.9</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.41 (0.80-2.25)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2004,17 +2004,17 @@
       <c r="E48" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="9" t="n">
-        <v>10.5</v>
+      <c r="F48" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.50 (0.92-5.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2059,7 +2059,7 @@
         <v>21</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.95 (0.73-1.30)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2096,7 +2096,7 @@
         <v>5</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.80-1.00)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2133,7 +2133,7 @@
         <v>15</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.50-0.97)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2170,7 +2170,7 @@
         <v>6</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.42-1.25)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2207,7 +2207,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>9.4</v>
+        <v>14.9</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.58-1.75)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2244,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.00-5.00)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2335,12 +2335,12 @@
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2385,7 +2385,7 @@
         <v>3</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.25 (0.50-4.00)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2422,7 +2422,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>16.3</v>
+        <v>26.6</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.64-1.28)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2459,12 +2459,12 @@
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2492,7 +2492,7 @@
         <v>48</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>64</v>
+        <v>45.9</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.31-1.88)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2529,12 +2529,12 @@
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2579,7 +2579,7 @@
         <v>4</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.34 (1.33-3.67)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2616,12 +2616,12 @@
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2649,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.96 (0.75-3.20)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>443.3</v>
+        <v>379.3</v>
       </c>
     </row>
   </sheetData>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-072, 23-032, 23-040, 23-045, 23-047</t>
+          <t>25-072, 23-045, 23-047, 23-046, 23-048</t>
         </is>
       </c>
     </row>
@@ -4415,28 +4415,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-032</t>
+          <t>23-045</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-040</t>
+          <t>23-047</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-045</t>
+          <t>23-046</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-047</t>
+          <t>23-048</t>
         </is>
       </c>
     </row>
@@ -4495,15 +4495,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4521,15 +4525,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4543,7 +4551,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4552,12 +4560,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.33-1.17)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-032</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4581,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4582,12 +4590,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.33-1.10)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4611,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4612,12 +4620,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4641,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4642,12 +4650,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4671,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4672,12 +4680,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4701,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4702,12 +4710,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-2.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4731,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4732,12 +4740,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-2.00)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4753,21 +4761,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.33 (n=2)</t>
+          <t>group_total:23h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-072, 23-040</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4791,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33.6</v>
+        <v>24.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4792,12 +4800,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.80-1.32)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -4813,21 +4821,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.22 (n=1)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-072</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4851,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4852,12 +4860,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=0.93 (0.25-1.17)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4881,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4882,12 +4890,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4911,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4912,12 +4920,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -4933,21 +4941,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-072, 23-040</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -4967,15 +4975,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4989,7 +5001,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>28.5</v>
+        <v>19.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4998,12 +5010,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=0.79 (0.61-1.80)</t>
+          <t>group_total:37h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5031,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>17.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5028,12 +5040,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.33)</t>
+          <t>group_total:37h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5049,21 +5061,21 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.3</v>
+        <v>5.8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.30 (n=2)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-072, 23-040</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5083,15 +5095,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5105,7 +5121,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5114,12 +5130,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.78 (1.00-2.50)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5151,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5144,12 +5160,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-4.38)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5181,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5174,12 +5190,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.60 (1.00-1.98)</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5211,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.7</v>
+        <v>12.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5204,12 +5220,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=1.10 (0.89-1.32)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5229,15 +5245,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5251,7 +5271,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5260,12 +5280,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=1.36 (0.93-1.71)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5301,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>20.6</v>
+        <v>9.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,12 +5310,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.47 (1.19-1.56)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5331,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>15.1</v>
+        <v>11.3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5320,12 +5340,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.08 (0.50-1.67)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5341,21 +5361,21 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=0.73 (n=2)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-072, 23-040</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5371,21 +5391,21 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14.7</v>
+        <v>4.4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.23 (n=2)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-072, 23-040</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5401,21 +5421,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.88 (n=2)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>23-047, 23-040</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5435,15 +5455,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5457,7 +5481,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5466,12 +5490,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.44 (1.00-2.50)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5511,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>19.7</v>
+        <v>22.9</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,12 +5520,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.41 (0.80-2.25)</t>
+          <t>group_total:82h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5517,21 +5541,21 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=3.50 (0.92-5.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5571,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5556,12 +5580,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=0.95 (0.73-1.30)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5601,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,12 +5610,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.80-1.00)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-072, 23-040, 23-032</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5631,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5616,12 +5640,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.50-0.97)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5661,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5646,12 +5670,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.42-1.25)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5691,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.4</v>
+        <v>14.9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5676,12 +5700,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.58-1.75)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5721,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5706,12 +5730,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5751,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5736,12 +5760,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.00-5.00)</t>
+          <t>group_total:54h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-072, 23-045, 23-040, 23-032</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5761,15 +5785,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5783,7 +5811,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5792,12 +5820,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=2.25 (0.50-4.00)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5841,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>16.3</v>
+        <v>26.6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5822,12 +5850,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.64-1.28)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5847,15 +5875,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5869,7 +5901,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>64</v>
+        <v>45.9</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5878,12 +5910,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.31-1.88)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-040, 23-032</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5903,15 +5935,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5925,7 +5961,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5934,12 +5970,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=2.34 (1.33-3.67)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-032</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5959,15 +5995,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5981,7 +6021,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5990,12 +6030,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ratio=1.96 (0.75-3.20)</t>
+          <t>group_total:98h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-072, 23-047, 23-045, 23-032</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-073 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-073 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>10.2</v>
+        <v>8.9</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -788,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -862,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -899,7 +899,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -973,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1027,7 +1027,7 @@
         <v>28</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>24.9</v>
+        <v>22.3</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1064,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1118,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1209,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1246,7 +1246,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1333,7 +1333,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:37h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1370,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>group_total:37h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1424,7 +1424,7 @@
         <v>11</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1531,7 +1531,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1568,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1622,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>group_total:13h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1676,7 +1676,7 @@
         <v>14</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>16.5</v>
+        <v>18.8</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1713,7 +1713,7 @@
         <v>14</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>9.6</v>
+        <v>10.9</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1750,7 +1750,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>11.3</v>
+        <v>12.9</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1787,7 +1787,7 @@
         <v>12</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1824,7 +1824,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1861,7 +1861,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1931,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>9.9</v>
+        <v>11.3</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1968,7 +1968,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>22.9</v>
+        <v>26.1</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2059,7 +2059,7 @@
         <v>21</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2096,7 +2096,7 @@
         <v>5</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2133,7 +2133,7 @@
         <v>15</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2170,7 +2170,7 @@
         <v>6</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2207,7 +2207,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>14.9</v>
+        <v>12.9</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2244,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2385,7 +2385,7 @@
         <v>3</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2422,7 +2422,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>26.6</v>
+        <v>29.9</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2492,7 +2492,7 @@
         <v>48</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>45.9</v>
+        <v>51.6</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2579,7 +2579,7 @@
         <v>4</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2649,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>379.3</v>
+        <v>382.1</v>
       </c>
     </row>
   </sheetData>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.2</v>
+        <v>8.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:23h</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.9</v>
+        <v>22.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:27h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:37h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:37h</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:26h</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>group_total:13h</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.5</v>
+        <v>18.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.6</v>
+        <v>10.9</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11.3</v>
+        <v>12.9</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9.9</v>
+        <v>11.3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22.9</v>
+        <v>26.1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:82h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>14.9</v>
+        <v>12.9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>group_total:54h</t>
+          <t>group_total:47h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>26.6</v>
+        <v>29.9</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>45.9</v>
+        <v>51.6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>group_total:98h</t>
+          <t>group_total:110h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
